--- a/stories/arbres/TREE-TMP-008.xlsx
+++ b/stories/arbres/TREE-TMP-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Il fait froid. Il pleut. Adam est dans l'entrée avec maman. Maman tend le manteau. Adam le met. Maman tend les bottes. Adam les met. Maman dit : froid, le manteau. Pluie, les bottes. Adam donne la main.</t>
+          <t>Il fait froid. Il pleut. Adam est dans l'entrée avec maman. Maman tend le manteau. Adam le met. Maman tend les bottes. Adam les met. Froid, le manteau. Pluie, les bottes. Adam donne la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait froid. Il pleut. Adam est dans l'entrée avec maman. Maman tend le manteau. Adam le met. Maman tend les bottes. Adam les met.
+maman|Froid, le manteau. Pluie, les bottes.
+narrateur|Adam donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'entrée, le jardin, ou le balcon.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dans l'entrée, Adam enfile le manteau. Il met les bottes. Il fait froid. Il pleut. Maman dit : on est prêts.</t>
+          <t>Dans l'entrée, Adam enfile le manteau. Il met les bottes. Il fait froid. Il pleut. On est prêts.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'entrée, Adam enfile le manteau. Il met les bottes. Il fait froid. Il pleut.
+maman|On est prêts.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'entrée, que met Adam ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2232,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2399,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Le ciel est gris. Adam serre le manteau. Ses bottes sont au sec. Froid. Pluie. Maman ouvre le parapluie.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2594,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2761,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2928,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3095,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3262,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3429,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3596,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3535,7 +3625,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le vent froid arrive. Adam a le manteau. Il a les bottes. Maman dit : on marche doucement.</t>
+          <t>Le vent froid arrive. Adam a le manteau. Il a les bottes. On marche doucement.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3673,6 +3763,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le vent froid arrive. Adam a le manteau. Il a les bottes.
+maman|On marche doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3863,6 +3959,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4025,6 +4126,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4293,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4460,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4627,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4794,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4961,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5128,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Les flaques brillent. Adam marche avec les bottes. Le manteau est chaud. Pluie. Froid.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,6 +5323,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5349,6 +5490,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5657,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5824,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5991,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6158,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6325,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6321,6 +6492,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, l'herbe est mouillée. Adam a le manteau. Il a les bottes. Froid et pluie. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6673,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, que met Adam ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6846,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Froid, le manteau. Pluie, les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6857,6 +7043,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
         </is>
       </c>
     </row>
@@ -7017,6 +7208,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, le ciel gris. Manteau. Bottes. Adam touche une feuille mouillée.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7207,6 +7403,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7369,6 +7570,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7737,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7904,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8071,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8238,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8405,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8572,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le vent froid au jardin. Adam garde le manteau. Les bottes tapent l'herbe. Pluie fine.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8531,6 +8767,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8693,6 +8934,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9101,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9268,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9435,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9602,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9769,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9936,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Une flaque au jardin. Adam la contourne avec les bottes. Le manteau reste fermé. Froid.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9855,6 +10131,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10017,6 +10298,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10465,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10632,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10799,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10966,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11133,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10989,6 +11300,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le balcon, l'eau tombe. Adam garde le manteau. Ses bottes tapent le sol. Froid. Pluie. Maman tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11481,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le balcon, que met Adam ?</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11654,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est habillé pour le froid et la pluie. Manteau. Bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11525,6 +11851,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
         </is>
       </c>
     </row>
@@ -11689,6 +12020,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Du balcon, le ciel gris. Adam a le manteau. Les bottes sont prêtes. Pluie. Froid.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11879,6 +12215,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12041,6 +12382,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12203,6 +12549,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12365,6 +12716,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12527,6 +12883,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12689,6 +13050,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12851,6 +13217,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13013,6 +13384,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le vent froid sur le balcon. Adam serre le manteau. Bottes aux pieds. Maman est près.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13203,6 +13579,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13365,6 +13746,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13527,6 +13913,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13689,6 +14080,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13851,6 +14247,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14013,6 +14414,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14175,6 +14581,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14337,6 +14748,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Les flaques se voient du balcon. Adam a les bottes. Le manteau. Pluie. Froid.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14527,6 +14943,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14689,6 +15110,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14851,6 +15277,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15013,6 +15444,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15175,6 +15611,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15337,6 +15778,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15499,6 +15945,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15517,7 +15968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15541,6 +15992,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-008.xlsx
+++ b/stories/arbres/TREE-TMP-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Adam donne la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre l'entrée, le jardin, ou le balcon.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1688,6 +1695,7 @@
 maman|On est prêts.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|Dans l'entrée, que met Adam ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2237,6 +2247,7 @@
           <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2404,6 +2415,7 @@
           <t>narrateur|Le ciel est gris. Adam serre le manteau. Ses bottes sont au sec. Froid. Pluie. Maman ouvre le parapluie.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -2766,6 +2783,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2933,6 +2951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3100,6 +3119,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3267,6 +3287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3455,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3769,6 +3796,7 @@
 maman|On marche doucement.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3962,6 +3990,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -4131,6 +4164,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4298,6 +4332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4465,6 +4500,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4632,6 +4668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4799,6 +4836,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4966,6 +5008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5133,6 +5176,7 @@
           <t>narrateur|Les flaques brillent. Adam marche avec les bottes. Le manteau est chaud. Pluie. Froid.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5326,6 +5370,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -5495,6 +5544,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5662,6 +5712,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5829,6 +5880,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5996,6 +6048,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6163,6 +6216,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis l'entrée, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6330,6 +6388,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6497,6 +6556,7 @@
           <t>narrateur|Au jardin, l'herbe est mouillée. Adam a le manteau. Il a les bottes. Froid et pluie. Maman est là.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6680,6 +6740,7 @@
           <t>narrateur|Au jardin, que met Adam ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6851,6 +6912,7 @@
           <t>narrateur|Oui. Froid, le manteau. Pluie, les bottes.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7050,6 +7112,7 @@
           <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7213,6 +7276,7 @@
           <t>narrateur|Au jardin, le ciel gris. Manteau. Bottes. Adam touche une feuille mouillée.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7470,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -7575,6 +7644,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7742,6 +7812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7909,6 +7980,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8076,6 +8148,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8243,6 +8316,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8410,6 +8488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8577,6 +8656,7 @@
           <t>narrateur|Le vent froid au jardin. Adam garde le manteau. Les bottes tapent l'herbe. Pluie fine.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8850,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -8939,6 +9024,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9106,6 +9192,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9273,6 +9360,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9440,6 +9528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9607,6 +9696,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9774,6 +9868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9941,6 +10036,7 @@
           <t>narrateur|Une flaque au jardin. Adam la contourne avec les bottes. Le manteau reste fermé. Froid.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10230,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -10303,6 +10404,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10470,6 +10572,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10637,6 +10740,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10804,6 +10908,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10971,6 +11076,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le jardin, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11138,6 +11248,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11305,6 +11416,7 @@
           <t>narrateur|Sur le balcon, l'eau tombe. Adam garde le manteau. Ses bottes tapent le sol. Froid. Pluie. Maman tient sa main.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11488,6 +11600,7 @@
           <t>narrateur|Sur le balcon, que met Adam ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11659,6 +11772,7 @@
           <t>narrateur|Adam est habillé pour le froid et la pluie. Manteau. Bottes.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11858,6 +11972,7 @@
           <t>narrateur|On peut prendre le ciel gris, le vent froid, ou les flaques.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12025,6 +12140,7 @@
           <t>narrateur|Du balcon, le ciel gris. Adam a le manteau. Les bottes sont prêtes. Pluie. Froid.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12218,6 +12334,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -12387,6 +12508,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12554,6 +12676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12721,6 +12844,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12888,6 +13012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13055,6 +13180,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le ciel gris. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13222,6 +13352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13389,6 +13520,7 @@
           <t>narrateur|Le vent froid sur le balcon. Adam serre le manteau. Bottes aux pieds. Maman est près.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13582,6 +13714,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -13751,6 +13888,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13918,6 +14056,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14085,6 +14224,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14252,6 +14392,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14419,6 +14560,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec le vent froid. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14586,6 +14732,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14753,6 +14900,7 @@
           <t>narrateur|Les flaques se voient du balcon. Adam a les bottes. Le manteau. Pluie. Froid.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14946,6 +15094,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le marché, l'école, ou le parc.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -15115,6 +15268,7 @@
           <t>narrateur|Adam va vers le marché. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15282,6 +15436,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15449,6 +15604,7 @@
           <t>narrateur|Adam va vers l'école. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15616,6 +15772,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15783,6 +15940,11 @@
           <t>narrateur|Adam va vers le parc. Il a le manteau. Il a les bottes. Froid et pluie, depuis le balcon, avec les flaques. Maman donne la main.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15950,6 +16112,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15968,7 +16131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16162,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16377,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
